--- a/data/trans_camb/IP2005-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 13,24</t>
+          <t>1,26; 13,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 16,03</t>
+          <t>4,0; 15,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,92; -0,99</t>
+          <t>-22,33; -1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,76</t>
+          <t>2,11; 11,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 13,57</t>
+          <t>3,92; 12,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 0,24</t>
+          <t>-17,96; 0,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,35</t>
+          <t>2,7; 10,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,94</t>
+          <t>4,88; 12,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -3,37</t>
+          <t>-17,55; -3,34</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 15,61</t>
+          <t>1,35; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 19,23</t>
+          <t>4,2; 18,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -1,2</t>
+          <t>-23,96; -2,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 13,75</t>
+          <t>2,2; 13,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 15,7</t>
+          <t>4,08; 14,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 0,16</t>
+          <t>-19,3; 0,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,69</t>
+          <t>2,91; 12,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 13,62</t>
+          <t>5,17; 13,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,14; -3,84</t>
+          <t>-18,83; -3,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 3,13</t>
+          <t>-4,32; 3,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 6,39</t>
+          <t>-1,55; 5,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -0,42</t>
+          <t>-10,04; -0,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,82</t>
+          <t>-1,74; 5,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,98</t>
+          <t>0,83; 7,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 0,98</t>
+          <t>-9,08; 0,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,6</t>
+          <t>-1,74; 3,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,77</t>
+          <t>0,94; 5,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -0,89</t>
+          <t>-8,04; -1,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,44</t>
+          <t>-4,57; 4,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 7,13</t>
+          <t>-1,61; 6,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,73; -0,56</t>
+          <t>-10,67; -0,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,52</t>
+          <t>-1,83; 6,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 8,88</t>
+          <t>0,93; 8,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 1,08</t>
+          <t>-9,65; 0,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,97</t>
+          <t>-1,85; 3,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,32</t>
+          <t>1,01; 6,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -1,01</t>
+          <t>-8,64; -1,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 11,42</t>
+          <t>-2,05; 11,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 14,79</t>
+          <t>2,83; 15,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 11,21</t>
+          <t>-2,5; 11,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 9,44</t>
+          <t>-4,09; 9,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 6,74</t>
+          <t>-6,29; 6,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 7,58</t>
+          <t>-4,9; 8,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,18</t>
+          <t>-1,64; 8,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 9,2</t>
+          <t>-0,09; 9,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,63</t>
+          <t>-2,11; 7,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 14,53</t>
+          <t>-2,44; 15,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 19,0</t>
+          <t>3,22; 20,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 14,11</t>
+          <t>-2,89; 14,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 11,83</t>
+          <t>-4,66; 11,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 8,25</t>
+          <t>-7,06; 8,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 9,19</t>
+          <t>-5,57; 10,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 10,03</t>
+          <t>-1,88; 9,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 11,52</t>
+          <t>-0,1; 11,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 9,31</t>
+          <t>-2,42; 9,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 5,15</t>
+          <t>-6,61; 5,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 7,94</t>
+          <t>-2,9; 7,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 8,0</t>
+          <t>-2,55; 8,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 4,91</t>
+          <t>-7,24; 4,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 6,1</t>
+          <t>-5,72; 6,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 9,29</t>
+          <t>-1,37; 9,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,37</t>
+          <t>-4,66; 3,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,62</t>
+          <t>-2,48; 5,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 6,72</t>
+          <t>-0,49; 6,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 6,12</t>
+          <t>-7,42; 6,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 9,49</t>
+          <t>-3,18; 9,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 9,49</t>
+          <t>-2,81; 9,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 5,86</t>
+          <t>-8,01; 5,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 7,29</t>
+          <t>-6,44; 7,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 11,36</t>
+          <t>-1,53; 10,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 4,0</t>
+          <t>-5,33; 4,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,68</t>
+          <t>-2,8; 6,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 7,97</t>
+          <t>-0,49; 8,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,21</t>
+          <t>-1,24; 4,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,89</t>
+          <t>1,89; 7,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,73</t>
+          <t>-4,18; 2,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,65</t>
+          <t>-0,52; 4,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,01</t>
+          <t>-0,46; 4,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,14</t>
+          <t>-3,89; 2,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,53</t>
+          <t>-0,16; 3,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,18</t>
+          <t>1,47; 5,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,14</t>
+          <t>-3,15; 1,25</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,85</t>
+          <t>-1,37; 4,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,9</t>
+          <t>2,07; 8,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 1,97</t>
+          <t>-4,64; 2,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,34</t>
+          <t>-0,62; 5,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,77</t>
+          <t>-0,52; 5,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,44</t>
+          <t>-4,33; 2,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,99</t>
+          <t>-0,18; 4,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,94</t>
+          <t>1,64; 6,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,29</t>
+          <t>-3,55; 1,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,59</t>
+          <t>1,12; 13,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 15,24</t>
+          <t>3,87; 15,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,33; -1,73</t>
+          <t>-23,05; -1,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,56</t>
+          <t>2,0; 11,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,35</t>
+          <t>3,52; 13,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 0,04</t>
+          <t>-17,22; 0,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 10,55</t>
+          <t>2,43; 10,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,09</t>
+          <t>4,71; 11,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,55; -3,34</t>
+          <t>-16,95; -2,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 16,25</t>
+          <t>1,17; 15,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 18,15</t>
+          <t>4,09; 17,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -2,26</t>
+          <t>-24,61; -1,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 13,1</t>
+          <t>2,08; 13,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 14,09</t>
+          <t>3,65; 15,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 0,01</t>
+          <t>-18,47; 0,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,12</t>
+          <t>2,53; 11,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,79</t>
+          <t>4,96; 13,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,83; -3,74</t>
+          <t>-18,31; -3,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,64</t>
+          <t>-4,88; 3,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,92</t>
+          <t>-1,37; 6,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -0,17</t>
+          <t>-10,33; -0,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 5,6</t>
+          <t>-1,83; 5,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,42</t>
+          <t>0,77; 7,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 0,67</t>
+          <t>-8,89; 0,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,48</t>
+          <t>-2,13; 3,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,89</t>
+          <t>0,55; 5,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -1,06</t>
+          <t>-7,78; -0,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 4,03</t>
+          <t>-5,26; 3,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 6,52</t>
+          <t>-1,46; 6,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -0,26</t>
+          <t>-11,03; -0,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,31</t>
+          <t>-1,95; 6,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,29</t>
+          <t>0,8; 8,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 0,8</t>
+          <t>-9,64; 0,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,86</t>
+          <t>-2,28; 3,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,51</t>
+          <t>0,54; 6,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -1,18</t>
+          <t>-8,39; -1,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 11,91</t>
+          <t>-2,29; 11,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 15,56</t>
+          <t>2,88; 14,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 11,48</t>
+          <t>-2,39; 11,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,72</t>
+          <t>-4,04; 8,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 6,72</t>
+          <t>-5,95; 7,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 8,24</t>
+          <t>-5,01; 7,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 8,06</t>
+          <t>-1,48; 8,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 9,26</t>
+          <t>0,11; 9,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,31</t>
+          <t>-2,02; 7,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 15,2</t>
+          <t>-2,58; 14,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 20,0</t>
+          <t>3,34; 18,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 14,44</t>
+          <t>-2,77; 14,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 11,96</t>
+          <t>-4,52; 11,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 8,28</t>
+          <t>-6,71; 8,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 10,12</t>
+          <t>-5,81; 9,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 9,94</t>
+          <t>-1,63; 9,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 11,49</t>
+          <t>0,15; 11,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 9,12</t>
+          <t>-2,31; 9,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 5,24</t>
+          <t>-6,61; 5,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,63</t>
+          <t>-2,86; 7,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 8,3</t>
+          <t>-2,67; 7,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 4,65</t>
+          <t>-6,86; 4,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 6,26</t>
+          <t>-5,78; 6,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 9,0</t>
+          <t>-1,34; 9,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 3,44</t>
+          <t>-4,62; 3,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,52</t>
+          <t>-2,61; 5,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,87</t>
+          <t>-0,3; 6,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 6,26</t>
+          <t>-7,4; 6,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 9,22</t>
+          <t>-3,18; 9,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 9,97</t>
+          <t>-2,94; 9,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 5,56</t>
+          <t>-7,88; 5,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 7,4</t>
+          <t>-6,56; 7,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 10,97</t>
+          <t>-1,51; 10,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,08</t>
+          <t>-5,25; 4,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,58</t>
+          <t>-2,9; 6,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,14</t>
+          <t>-0,32; 8,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,18</t>
+          <t>-1,18; 4,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,08</t>
+          <t>1,95; 7,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,23</t>
+          <t>-3,98; 2,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,81</t>
+          <t>-0,38; 4,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,84</t>
+          <t>-0,5; 5,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,14</t>
+          <t>-3,93; 2,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,62</t>
+          <t>-0,06; 3,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,31</t>
+          <t>1,53; 5,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,25</t>
+          <t>-2,92; 1,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,76</t>
+          <t>-1,31; 4,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,16</t>
+          <t>2,17; 8,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,56</t>
+          <t>-4,41; 2,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,52</t>
+          <t>-0,42; 5,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,51</t>
+          <t>-0,56; 5,87</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,44</t>
+          <t>-4,34; 2,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,12</t>
+          <t>-0,07; 4,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,03</t>
+          <t>1,71; 6,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,42</t>
+          <t>-3,25; 1,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-8,48</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-11,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,37</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,07</t>
+          <t>-11,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,92</t>
+          <t>-10,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 13,51</t>
+          <t>1,47; 11,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 15,06</t>
+          <t>3,99; 13,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,05; -1,47</t>
+          <t>-17,54; 0,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,74</t>
+          <t>1,07; 13,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 13,12</t>
+          <t>3,7; 16,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 0,81</t>
+          <t>-23,56; -1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,11</t>
+          <t>2,51; 10,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,8</t>
+          <t>4,7; 11,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,95; -2,84</t>
+          <t>-17,58; -3,84</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-9,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,14%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>9,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-12,69%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-8,71%</t>
+          <t>-13,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,81%</t>
+          <t>-11,35%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 15,84</t>
+          <t>1,67; 13,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 17,9</t>
+          <t>4,16; 15,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,61; -1,67</t>
+          <t>-18,73; 0,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 13,41</t>
+          <t>1,16; 15,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 15,1</t>
+          <t>3,94; 19,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 0,61</t>
+          <t>-25,09; -1,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 11,45</t>
+          <t>2,63; 11,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,45</t>
+          <t>4,94; 13,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -3,31</t>
+          <t>-18,78; -4,28</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,73</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,49</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,19</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-5,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,25</t>
+          <t>-4,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,22</t>
+          <t>-1,45; 5,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 6,22</t>
+          <t>1,07; 7,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,33; -0,59</t>
+          <t>-9,2; 0,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,68</t>
+          <t>-4,91; 3,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,48</t>
+          <t>-1,29; 6,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 0,63</t>
+          <t>-10,68; -1,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,33</t>
+          <t>-2,0; 3,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,91</t>
+          <t>0,91; 5,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -0,93</t>
+          <t>-7,93; -1,06</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-4,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-0,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-3,94%</t>
+          <t>-5,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,62%</t>
+          <t>-4,97%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,53</t>
+          <t>-1,56; 6,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 6,84</t>
+          <t>1,09; 8,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,03; -0,69</t>
+          <t>-9,84; 1,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,35</t>
+          <t>-5,18; 3,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,37</t>
+          <t>-1,35; 7,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 0,6</t>
+          <t>-11,41; -1,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,69</t>
+          <t>-2,13; 3,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,5</t>
+          <t>0,95; 6,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,39; -1,0</t>
+          <t>-8,7; -1,27</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,8</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,4</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 11,26</t>
+          <t>-4,18; 9,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 14,61</t>
+          <t>-6,28; 6,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 11,31</t>
+          <t>-5,66; 7,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 8,93</t>
+          <t>-2,04; 11,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 7,15</t>
+          <t>2,87; 14,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 7,98</t>
+          <t>-3,19; 11,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,01</t>
+          <t>-1,5; 8,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,06</t>
+          <t>0,13; 9,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 7,38</t>
+          <t>-2,63; 7,3</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5,14%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>10,55%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 14,14</t>
+          <t>-4,72; 11,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 18,66</t>
+          <t>-7,24; 8,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 14,59</t>
+          <t>-6,41; 8,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 11,21</t>
+          <t>-2,39; 14,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 8,87</t>
+          <t>3,25; 19,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 9,96</t>
+          <t>-3,56; 13,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 9,87</t>
+          <t>-1,75; 10,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 11,22</t>
+          <t>0,26; 11,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 9,13</t>
+          <t>-3,06; 9,04</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,54</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,41</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,69</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>2,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 5,16</t>
+          <t>-6,12; 4,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 7,75</t>
+          <t>-5,66; 6,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 7,65</t>
+          <t>-1,43; 9,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 4,37</t>
+          <t>-6,13; 5,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 6,43</t>
+          <t>-3,37; 7,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 9,11</t>
+          <t>-3,34; 6,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,84</t>
+          <t>-4,76; 3,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 5,33</t>
+          <t>-2,84; 5,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,92</t>
+          <t>-0,93; 6,11</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-0,76%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-0,59%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-0,76%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 6,14</t>
+          <t>-6,81; 5,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 9,23</t>
+          <t>-6,37; 7,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 9,06</t>
+          <t>-1,63; 11,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 5,18</t>
+          <t>-6,92; 6,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,74</t>
+          <t>-3,72; 9,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 10,87</t>
+          <t>-3,7; 8,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,49</t>
+          <t>-5,46; 4,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 6,29</t>
+          <t>-3,18; 6,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 8,22</t>
+          <t>-1,04; 7,22</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,08</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>4,39</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,09</t>
+          <t>-0,7; 4,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,03</t>
+          <t>-0,4; 5,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,17</t>
+          <t>-3,88; 2,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,76</t>
+          <t>-1,26; 4,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,09</t>
+          <t>1,69; 6,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,19</t>
+          <t>-4,88; 1,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,77</t>
+          <t>-0,23; 3,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,27</t>
+          <t>1,42; 5,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,37</t>
+          <t>-3,3; 0,73</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-1,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-1,15%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,93%</t>
+          <t>-1,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,03%</t>
+          <t>-1,41%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,66</t>
+          <t>-0,77; 5,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,08</t>
+          <t>-0,45; 5,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,46</t>
+          <t>-4,31; 2,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,46</t>
+          <t>-1,4; 4,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,87</t>
+          <t>1,88; 7,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,52</t>
+          <t>-5,4; 1,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,31</t>
+          <t>-0,26; 3,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,01</t>
+          <t>1,58; 5,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,56</t>
+          <t>-3,66; 0,83</t>
         </is>
       </c>
     </row>
